--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484706_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484706_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.984999999999999</v>
+        <v>8.087300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5448</v>
+        <v>4.3499</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4402</v>
+        <v>3.7374</v>
       </c>
       <c r="G2" t="n">
         <v>6.8632</v>
@@ -610,13 +610,13 @@
         <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9855</v>
+        <v>0.0878</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4442</v>
+        <v>0.2493</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4587</v>
+        <v>-0.1614</v>
       </c>
       <c r="V2" t="n">
         <v>-0.513</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.545199999999999</v>
+        <v>7.5744</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1662</v>
+        <v>2.7405</v>
       </c>
       <c r="F3" t="n">
-        <v>5.379</v>
+        <v>4.834</v>
       </c>
       <c r="G3" t="n">
         <v>7.7414</v>
@@ -688,13 +688,13 @@
         <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2776</v>
+        <v>1.3069</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9684</v>
+        <v>0.5426</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3093</v>
+        <v>0.7643</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1911</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3187</v>
+        <v>4.3154</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6583</v>
+        <v>2.0018</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6604</v>
+        <v>2.3136</v>
       </c>
       <c r="G4" t="n">
         <v>1.3574</v>
@@ -766,13 +766,13 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2099</v>
+        <v>0.2066</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5505</v>
+        <v>-0.207</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7605</v>
+        <v>0.4136</v>
       </c>
       <c r="V4" t="n">
         <v>2.2016</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.442</v>
+        <v>3.2216</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8649</v>
+        <v>2.0161</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5771</v>
+        <v>1.2055</v>
       </c>
       <c r="G5" t="n">
         <v>5.2662</v>
@@ -844,13 +844,13 @@
         <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4506</v>
+        <v>0.2302</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1267</v>
+        <v>0.2779</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3239</v>
+        <v>-0.0477</v>
       </c>
       <c r="V5" t="n">
         <v>-2.0915</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7745</v>
+        <v>2.2419</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7076</v>
+        <v>-0.3641</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4821</v>
+        <v>2.606</v>
       </c>
       <c r="G6" t="n">
         <v>0.6814</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7236</v>
+        <v>-0.2562</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7157</v>
+        <v>-0.3722</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.1159</v>
       </c>
       <c r="V6" t="n">
         <v>1.267</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SAEZ CUARTERO</t>
+          <t>Q. GJENERALI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3701</v>
+        <v>1.124</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3897</v>
+        <v>-1.1761</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0196</v>
+        <v>2.3001</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1499</v>
+        <v>0.9028</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4863</v>
+        <v>1.1723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6636</v>
+        <v>-0.2694</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4262</v>
+        <v>0.1294</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8269</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5994</v>
+        <v>-0.5577</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7237</v>
+        <v>0.7735</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6594</v>
+        <v>0.4852</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0643</v>
+        <v>0.2882</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3665</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4546</v>
+        <v>-0.4802</v>
       </c>
       <c r="T7" t="n">
-        <v>0.549</v>
+        <v>-0.4962</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0944</v>
+        <v>0.016</v>
       </c>
       <c r="V7" t="n">
-        <v>1.699</v>
+        <v>2.5339</v>
       </c>
       <c r="W7" t="n">
-        <v>1.267</v>
+        <v>2.8559</v>
       </c>
       <c r="X7" t="n">
-        <v>0.432</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q. GJENERALI</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2136</v>
+        <v>0.6069</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6158</v>
+        <v>-2.1428</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8294</v>
+        <v>2.7497</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9028</v>
+        <v>1.3504</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1723</v>
+        <v>2.0171</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2694</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1294</v>
+        <v>-1.1219</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6345</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5577</v>
+        <v>-1.7564</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7735</v>
+        <v>2.4723</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4852</v>
+        <v>1.3827</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2882</v>
+        <v>1.0896</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8326</v>
+        <v>2.0158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8326</v>
+        <v>2.9321</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3906</v>
+        <v>-1.1808</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9359</v>
+        <v>-0.437</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4547</v>
+        <v>-0.7438</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5339</v>
+        <v>-1.5785</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8559</v>
+        <v>0.3324</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3219</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>A. SAEZ CUARTERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4492</v>
+        <v>0.3786</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6787</v>
+        <v>0.3486</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2295</v>
+        <v>0.0299</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3504</v>
+        <v>-2.1499</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0171</v>
+        <v>-1.4863</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.6636</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1219</v>
+        <v>-1.4262</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6345</v>
+        <v>-0.8269</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7564</v>
+        <v>-0.5994</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4723</v>
+        <v>-0.7237</v>
       </c>
       <c r="N9" t="n">
-        <v>1.3827</v>
+        <v>-0.6594</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0896</v>
+        <v>-0.0643</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0158</v>
+        <v>0.3665</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9321</v>
+        <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.2369</v>
+        <v>0.463</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9728</v>
+        <v>0.5079</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.264</v>
+        <v>-0.0449</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5785</v>
+        <v>1.699</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3324</v>
+        <v>1.267</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9109</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5229</v>
+        <v>-0.3225</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2238</v>
+        <v>-3.8252</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7009</v>
+        <v>3.5027</v>
       </c>
       <c r="G10" t="n">
         <v>2.1644</v>
@@ -1234,13 +1234,13 @@
         <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0198</v>
+        <v>0.1806</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2036</v>
+        <v>0.195</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1838</v>
+        <v>-0.0144</v>
       </c>
       <c r="V10" t="n">
         <v>-0.835</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>26.677</v>
+        <v>27.2276</v>
       </c>
       <c r="E11" t="n">
-        <v>3.398000000000001</v>
+        <v>3.9487</v>
       </c>
       <c r="F11" t="n">
-        <v>23.279</v>
+        <v>23.2789</v>
       </c>
       <c r="G11" t="n">
         <v>24.1773</v>
@@ -1312,13 +1312,13 @@
         <v>16.4932</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0072999999999999</v>
+        <v>0.5579000000000002</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2902000000000002</v>
+        <v>0.2603</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2977999999999998</v>
+        <v>0.2975999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>2.4924</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4541</v>
+        <v>0.8567</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7596</v>
+        <v>1.1826</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3055</v>
+        <v>-0.3259</v>
       </c>
       <c r="G12" t="n">
         <v>1.9017</v>
@@ -1390,13 +1390,13 @@
         <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3587</v>
+        <v>-0.2387</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3273</v>
+        <v>-0.2496</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0313</v>
+        <v>0.0109</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6231</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.0706</v>
+        <v>-0.7488</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.4189</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2889</v>
+        <v>-0.3299</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.1258</v>
+        <v>-0.4068</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.1965</v>
+        <v>-0.6664</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0706</v>
+        <v>0.2596</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0388</v>
+        <v>1.2986</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.1737</v>
+        <v>0.622</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1349</v>
+        <v>0.6766</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.087</v>
+        <v>-1.7054</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0228</v>
+        <v>-1.2884</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0643</v>
+        <v>-0.417</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9163</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3783</v>
+        <v>0.6173</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3869</v>
+        <v>0.0472</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0086</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5172</v>
+        <v>0.5068</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6439</v>
+        <v>1.9005</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1267</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. LARIO ECHEVARRIAS</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.091</v>
+        <v>-0.8258</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2238</v>
+        <v>-0.6856</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8672</v>
+        <v>-0.1402</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.7912</v>
+        <v>-2.1258</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.7974</v>
+        <v>-2.1965</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9938</v>
+        <v>0.0706</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.793</v>
+        <v>-1.0388</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.793</v>
+        <v>-1.1737</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1349</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9982</v>
+        <v>-1.087</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0044</v>
+        <v>-1.0228</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9938</v>
+        <v>-0.0643</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1401</v>
+        <v>-0.1335</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2919</v>
+        <v>-0.2907</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1518</v>
+        <v>0.1572</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2774</v>
+        <v>0.5172</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2774</v>
+        <v>0.6439</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>P. LARIO ECHEVARRIAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3636</v>
+        <v>-1.0808</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7073</v>
+        <v>-0.4161</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6563</v>
+        <v>-0.6647</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4068</v>
+        <v>-3.7912</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6664</v>
+        <v>-2.7974</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2596</v>
+        <v>-0.9938</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2986</v>
+        <v>-1.793</v>
       </c>
       <c r="K16" t="n">
-        <v>0.622</v>
+        <v>-1.793</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6766</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7054</v>
+        <v>-1.9982</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2884</v>
+        <v>-1.0044</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.417</v>
+        <v>-0.9938</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1991</v>
+        <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0024</v>
+        <v>0.1503</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2413</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2437</v>
+        <v>0.0507</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5068</v>
+        <v>1.2774</v>
       </c>
       <c r="W16" t="n">
-        <v>1.9005</v>
+        <v>1.2774</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VIVES HURTADO</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7984</v>
+        <v>-1.4196</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0468</v>
+        <v>-1.5698</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8452</v>
+        <v>0.1502</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4461</v>
+        <v>-1.7534</v>
       </c>
       <c r="H17" t="n">
-        <v>0.054</v>
+        <v>-1.324</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5001</v>
+        <v>-0.4295</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7219</v>
+        <v>-1.1655</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2538</v>
+        <v>-1.217</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5319</v>
+        <v>0.0515</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.168</v>
+        <v>-0.5879</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1999</v>
+        <v>-0.1069</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0318</v>
+        <v>-0.481</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2587</v>
+        <v>0.6725</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4419</v>
+        <v>0.1901</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7006</v>
+        <v>0.4824</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0613</v>
+        <v>-1.0717</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5993</v>
+        <v>0.3219</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6606</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>A. VIVES HURTADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9513</v>
+        <v>-1.8786</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1467</v>
+        <v>0.2391</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1954</v>
+        <v>-2.1177</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7534</v>
+        <v>-0.4461</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.324</v>
+        <v>0.054</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4295</v>
+        <v>-0.5001</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1655</v>
+        <v>0.7219</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.217</v>
+        <v>1.2538</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0515</v>
+        <v>-0.5319</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5879</v>
+        <v>-1.168</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1069</v>
+        <v>-1.1999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.481</v>
+        <v>0.0318</v>
       </c>
       <c r="P18" t="n">
-        <v>0.733</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1408</v>
+        <v>0.1785</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3869</v>
+        <v>-0.2496</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.4281</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0717</v>
+        <v>-1.0613</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3219</v>
+        <v>1.5993</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3937</v>
+        <v>-2.6606</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.0119</v>
+        <v>-4.0002</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.1998</v>
+        <v>-5.2959</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1879</v>
+        <v>1.2957</v>
       </c>
       <c r="G19" t="n">
         <v>-5.0952</v>
@@ -1936,13 +1936,13 @@
         <v>2.5656</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0284</v>
+        <v>0.04</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.058</v>
+        <v>-0.1542</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0864</v>
+        <v>0.1942</v>
       </c>
       <c r="V19" t="n">
         <v>0.3219</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.433</v>
+        <v>-4.1314</v>
       </c>
       <c r="E20" t="n">
         <v>-4.0228</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4102</v>
+        <v>-0.1086</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9515</v>
@@ -2014,13 +2014,13 @@
         <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0209</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4223</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5986</v>
+        <v>-0.297</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6439</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2055</v>
+        <v>-5.2696</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5087</v>
+        <v>-4.701</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6968</v>
+        <v>-0.5686</v>
       </c>
       <c r="G21" t="n">
         <v>-5.3233</v>
@@ -2092,13 +2092,13 @@
         <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7496</v>
+        <v>0.6855</v>
       </c>
       <c r="T21" t="n">
-        <v>0.638</v>
+        <v>0.4457</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1116</v>
+        <v>0.2398</v>
       </c>
       <c r="V21" t="n">
         <v>-0.4486</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.8308</v>
+        <v>-7.5219</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.1195</v>
+        <v>-8.2156</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2887</v>
+        <v>0.6937</v>
       </c>
       <c r="G22" t="n">
         <v>-4.8108</v>
@@ -2170,13 +2170,13 @@
         <v>2.1991</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.287</v>
+        <v>0.0219</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3824</v>
+        <v>0.2862</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6694</v>
+        <v>-0.2643</v>
       </c>
       <c r="V22" t="n">
         <v>-1.267</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-26.6769</v>
+        <v>-25.3949</v>
       </c>
       <c r="E23" t="n">
         <v>-23.2789</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3981</v>
+        <v>-2.116000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-24.1773</v>
@@ -2224,7 +2224,7 @@
         <v>-11.3069</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.8982</v>
+        <v>-4.898199999999999</v>
       </c>
       <c r="L23" t="n">
         <v>-6.4088</v>
@@ -2239,7 +2239,7 @@
         <v>-2.8869</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.0001999999999997559</v>
+        <v>-0.000199999999999978</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.4932</v>
@@ -2248,13 +2248,13 @@
         <v>16.4931</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.007499999999999896</v>
+        <v>1.2745</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2977000000000002</v>
+        <v>-0.2976000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2900999999999999</v>
+        <v>1.5721</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4923</v>
@@ -2263,7 +2263,7 @@
         <v>4.818700000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.3111</v>
+        <v>-7.311100000000001</v>
       </c>
     </row>
   </sheetData>
